--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1-01-61</t>
+          <t>S1-01-G1</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alulce</t>
+          <t>Kgllc</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RLOLCLLELS TL</t>
+          <t>KOHCIJ</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G07D</t>
+          <t>G07C</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kgllc</t>
+          <t>Paule</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOHCIJ</t>
+          <t>ROHERT</t>
         </is>
       </c>
     </row>
@@ -744,10 +744,10 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>9.140000000000001</v>
+        <v>2.12</v>
       </c>
       <c r="K7" t="n">
-        <v>1111</v>
+        <v>1191</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paule</t>
+          <t>PAULE</t>
         </is>
       </c>
     </row>
@@ -711,9 +711,6 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>U</t>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62616.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -744,7 +744,7 @@
         <v>2.12</v>
       </c>
       <c r="K7" t="n">
-        <v>1191</v>
+        <v>19</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
